--- a/fpa_variance_analysis.xlsx
+++ b/fpa_variance_analysis.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.9%</t>
         </is>
       </c>
     </row>
